--- a/artfynd/A 56589-2024 artfynd.xlsx
+++ b/artfynd/A 56589-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86427153</v>
+        <v>86427169</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521457.375637289</v>
+        <v>521366</v>
       </c>
       <c r="R2" t="n">
-        <v>7203126.433408816</v>
+        <v>7203073</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,17 +759,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86427214</v>
+        <v>86426892</v>
       </c>
       <c r="B3" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521636.5699982677</v>
+        <v>521252</v>
       </c>
       <c r="R3" t="n">
-        <v>7203171.385565491</v>
+        <v>7202789</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,21 +855,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -898,21 +868,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -929,37 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86427212</v>
+        <v>86426920</v>
       </c>
       <c r="B4" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521352.7670901957</v>
+        <v>521445</v>
       </c>
       <c r="R4" t="n">
-        <v>7203096.011887145</v>
+        <v>7203145</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,21 +952,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1028,17 +968,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1056,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>86427215</v>
+        <v>86426921</v>
       </c>
       <c r="B5" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1096,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521676.2976486325</v>
+        <v>521433</v>
       </c>
       <c r="R5" t="n">
-        <v>7203194.139027351</v>
+        <v>7203112</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,21 +1064,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1155,17 +1080,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1183,15 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>86427126</v>
+        <v>86427183</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521439.3207313473</v>
+        <v>521653</v>
       </c>
       <c r="R6" t="n">
-        <v>7203158.518852546</v>
+        <v>7203184</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,21 +1176,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1279,6 +1189,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1295,15 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>86427206</v>
+        <v>86513354</v>
       </c>
       <c r="B7" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,37 +1231,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Klippen, Trappstegsforsen, Ås lm</t>
+          <t>Njakafjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521352.7731487972</v>
+        <v>521721</v>
       </c>
       <c r="R7" t="n">
-        <v>7203095.164152895</v>
+        <v>7203019</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1368,21 +1288,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1392,45 +1302,30 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>86427125</v>
+        <v>86426948</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1462,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521366.829174028</v>
+        <v>521367</v>
       </c>
       <c r="R8" t="n">
-        <v>7203206.745335115</v>
+        <v>7203207</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1495,19 +1390,9 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-06-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1534,37 +1419,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>86426920</v>
+        <v>86426949</v>
       </c>
       <c r="B9" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>498</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1574,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521444.9318588539</v>
+        <v>521462</v>
       </c>
       <c r="R9" t="n">
-        <v>7203145.418812103</v>
+        <v>7203168</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,21 +1487,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1630,21 +1500,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1661,15 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>86426880</v>
+        <v>86426964</v>
       </c>
       <c r="B10" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1701,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521699.1953613622</v>
+        <v>521425</v>
       </c>
       <c r="R10" t="n">
-        <v>7203138.353146709</v>
+        <v>7203210</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1734,21 +1584,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1760,17 +1600,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1788,53 +1628,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>86427064</v>
+        <v>86513351</v>
       </c>
       <c r="B11" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Klippen, Trappstegsforsen, Ås lm</t>
+          <t>Njakafjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521387.8483644046</v>
+        <v>521823</v>
       </c>
       <c r="R11" t="n">
-        <v>7203056.840898709</v>
+        <v>7202818</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1861,21 +1696,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1885,83 +1710,68 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>86427124</v>
+        <v>86513352</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Klippen, Trappstegsforsen, Ås lm</t>
+          <t>Njakafjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521253.5203328562</v>
+        <v>521597</v>
       </c>
       <c r="R12" t="n">
-        <v>7202788.817106419</v>
+        <v>7202909</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1988,21 +1798,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2011,31 +1811,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>86426726</v>
+        <v>86427153</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,39 +1843,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Klippen, Trappstegsforsen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521385.4028784108</v>
+        <v>521457</v>
       </c>
       <c r="R13" t="n">
-        <v>7202924.141529013</v>
+        <v>7203126</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2105,21 +1900,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2128,6 +1913,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2147,12 +1947,7 @@
         <v>86427154</v>
       </c>
       <c r="B14" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521459.6204815845</v>
+        <v>521460</v>
       </c>
       <c r="R14" t="n">
-        <v>7203168.413818073</v>
+        <v>7203168</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2217,19 +2012,9 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-06-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2271,15 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>86426964</v>
+        <v>86426815</v>
       </c>
       <c r="B15" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2311,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521425.3730847849</v>
+        <v>521447</v>
       </c>
       <c r="R15" t="n">
-        <v>7203209.707843639</v>
+        <v>7203145</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2344,21 +2124,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2367,21 +2137,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2398,37 +2153,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>86427169</v>
+        <v>86426880</v>
       </c>
       <c r="B16" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2438,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521365.662144613</v>
+        <v>521699</v>
       </c>
       <c r="R16" t="n">
-        <v>7203073.21399469</v>
+        <v>7203138</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2471,19 +2221,9 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-06-19</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2525,15 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>86426625</v>
+        <v>86426624</v>
       </c>
       <c r="B17" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2565,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521366.5109093825</v>
+        <v>521358</v>
       </c>
       <c r="R17" t="n">
-        <v>7203073.220064384</v>
+        <v>7203061</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2598,19 +2333,9 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-06-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2652,15 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>86427127</v>
+        <v>86426625</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2692,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521443.1370217601</v>
+        <v>521367</v>
       </c>
       <c r="R18" t="n">
-        <v>7203158.970120608</v>
+        <v>7203073</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2725,21 +2445,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2748,6 +2458,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2764,37 +2489,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>86426815</v>
+        <v>86426648</v>
       </c>
       <c r="B19" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2804,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521447.0537195831</v>
+        <v>521443</v>
       </c>
       <c r="R19" t="n">
-        <v>7203145.434043168</v>
+        <v>7203128</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2837,19 +2557,9 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2020-06-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2876,37 +2586,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>86427213</v>
+        <v>86427124</v>
       </c>
       <c r="B20" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2916,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521439.2690243002</v>
+        <v>521254</v>
       </c>
       <c r="R20" t="n">
-        <v>7203165.724433903</v>
+        <v>7202789</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2949,21 +2654,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2972,21 +2667,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3003,37 +2683,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>86427183</v>
+        <v>86427125</v>
       </c>
       <c r="B21" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3043,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521652.6069170255</v>
+        <v>521367</v>
       </c>
       <c r="R21" t="n">
-        <v>7203183.79420571</v>
+        <v>7203207</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3076,21 +2751,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3099,21 +2764,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3130,37 +2780,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>86426948</v>
+        <v>86427126</v>
       </c>
       <c r="B22" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3170,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521367.2505060661</v>
+        <v>521439</v>
       </c>
       <c r="R22" t="n">
-        <v>7203207.172221493</v>
+        <v>7203159</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3203,19 +2848,9 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2020-06-19</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3242,19 +2877,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>86427128</v>
+        <v>86427127</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3282,10 +2912,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521458.3412863417</v>
+        <v>521443</v>
       </c>
       <c r="R23" t="n">
-        <v>7203169.252387446</v>
+        <v>7203159</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3315,19 +2945,9 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2020-06-19</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3354,15 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>86426921</v>
+        <v>86427128</v>
       </c>
       <c r="B24" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3370,21 +2985,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3394,10 +3009,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521432.8622374768</v>
+        <v>521458</v>
       </c>
       <c r="R24" t="n">
-        <v>7203112.26923121</v>
+        <v>7203169</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3427,21 +3042,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3450,21 +3055,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3481,15 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>86427207</v>
+        <v>86427212</v>
       </c>
       <c r="B25" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3497,21 +3082,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3521,10 +3106,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521636.9912971281</v>
+        <v>521353</v>
       </c>
       <c r="R25" t="n">
-        <v>7203171.81249524</v>
+        <v>7203096</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3554,19 +3139,9 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2020-06-19</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3608,15 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>86426631</v>
+        <v>86427213</v>
       </c>
       <c r="B26" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3624,21 +3194,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3648,10 +3218,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521510.1325829125</v>
+        <v>521439</v>
       </c>
       <c r="R26" t="n">
-        <v>7203167.081547515</v>
+        <v>7203166</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3681,21 +3251,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3707,17 +3267,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3735,15 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>86426624</v>
+        <v>86427214</v>
       </c>
       <c r="B27" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3751,21 +3306,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3242</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3775,10 +3330,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521358.1081029065</v>
+        <v>521637</v>
       </c>
       <c r="R27" t="n">
-        <v>7203061.290986388</v>
+        <v>7203171</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3808,19 +3363,9 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2020-06-19</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3862,15 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>86426949</v>
+        <v>86427215</v>
       </c>
       <c r="B28" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3878,21 +3418,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3902,10 +3442,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521461.7484155536</v>
+        <v>521676</v>
       </c>
       <c r="R28" t="n">
-        <v>7203167.581345798</v>
+        <v>7203194</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3935,21 +3475,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3958,6 +3488,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3974,37 +3519,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>86426648</v>
+        <v>86426631</v>
       </c>
       <c r="B29" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4014,10 +3554,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521443.3560563792</v>
+        <v>521510</v>
       </c>
       <c r="R29" t="n">
-        <v>7203128.452176607</v>
+        <v>7203167</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4047,21 +3587,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4070,6 +3600,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4086,15 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>86513354</v>
+        <v>86427206</v>
       </c>
       <c r="B30" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4102,37 +3642,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6487</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Njakafjäll, Ås lm</t>
+          <t>Klippen, Trappstegsforsen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521720.8586186813</v>
+        <v>521353</v>
       </c>
       <c r="R30" t="n">
-        <v>7203018.973021335</v>
+        <v>7203096</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4159,21 +3699,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4183,35 +3713,40 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AS30" t="inlineStr">
-        <is>
-          <t>Anders Hällström</t>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>86513353</v>
+        <v>86427207</v>
       </c>
       <c r="B31" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4219,37 +3754,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6487</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Njakafjäll, Ås lm</t>
+          <t>Klippen, Trappstegsforsen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521595.8978131684</v>
+        <v>521637</v>
       </c>
       <c r="R31" t="n">
-        <v>7202926.927246253</v>
+        <v>7203172</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4276,21 +3811,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4300,35 +3825,40 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>Anders Hällström</t>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>86513351</v>
+        <v>86426726</v>
       </c>
       <c r="B32" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4336,37 +3866,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Njakafjäll, Ås lm</t>
+          <t>Klippen, Trappstegsforsen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521822.9127059915</v>
+        <v>521385</v>
       </c>
       <c r="R32" t="n">
-        <v>7202817.933204268</v>
+        <v>7202924</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4393,21 +3928,11 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4416,36 +3941,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AS32" t="inlineStr">
-        <is>
-          <t>Anders Hällström</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>86513352</v>
+        <v>88361994</v>
       </c>
       <c r="B33" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4453,37 +3968,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Njakafjäll, Ås lm</t>
+          <t>Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521596.8753026649</v>
+        <v>520783</v>
       </c>
       <c r="R33" t="n">
-        <v>7202909.1299044</v>
+        <v>7203805</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4507,22 +4022,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2020-06-19</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2020-06-19</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4533,36 +4038,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AS33" t="inlineStr">
-        <is>
-          <t>Anders Hällström</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Billy Lindblom, Alexina Brännlund, Emmy Ransgart, Mikael Sandström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>88404513</v>
+        <v>88404559</v>
       </c>
       <c r="B34" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4570,21 +4065,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4594,10 +4089,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520783.2827855822</v>
+        <v>521037</v>
       </c>
       <c r="R34" t="n">
-        <v>7203697.247096556</v>
+        <v>7203634</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4627,19 +4122,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4666,37 +4151,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>88404270</v>
+        <v>88362015</v>
       </c>
       <c r="B35" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>864</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4706,10 +4186,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521080.8142190702</v>
+        <v>520929</v>
       </c>
       <c r="R35" t="n">
-        <v>7203684.922787505</v>
+        <v>7203508</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4739,19 +4219,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4766,27 +4236,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Via Yasmine Kindlund</t>
+          <t>Billy Lindblom, Alexina Brännlund, Emmy Ransgart, Mikael Sandström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>88404512</v>
+        <v>88362018</v>
       </c>
       <c r="B36" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4794,21 +4259,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4818,10 +4283,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520796.6034832147</v>
+        <v>520965</v>
       </c>
       <c r="R36" t="n">
-        <v>7203734.210390692</v>
+        <v>7203561</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4851,19 +4316,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4878,27 +4333,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Via Yasmine Kindlund</t>
+          <t>Billy Lindblom, Alexina Brännlund, Emmy Ransgart, Mikael Sandström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>88361995</v>
+        <v>88362020</v>
       </c>
       <c r="B37" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4906,21 +4356,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4930,10 +4380,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520783.382398433</v>
+        <v>520999</v>
       </c>
       <c r="R37" t="n">
-        <v>7203804.891655518</v>
+        <v>7203608</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4963,19 +4413,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5002,15 +4442,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>88362021</v>
+        <v>88404431</v>
       </c>
       <c r="B38" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5018,21 +4453,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3242</v>
+        <v>864</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5042,10 +4477,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520999.9721688684</v>
+        <v>520947</v>
       </c>
       <c r="R38" t="n">
-        <v>7203595.776854476</v>
+        <v>7203520</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5075,19 +4510,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5102,27 +4527,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Billy Lindblom, Alexina Brännlund, Emmy Ransgart, Mikael Sandström</t>
+          <t>Via Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>88404431</v>
+        <v>88404441</v>
       </c>
       <c r="B39" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5130,21 +4550,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5154,10 +4574,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520946.6110389023</v>
+        <v>520762</v>
       </c>
       <c r="R39" t="n">
-        <v>7203520.385620572</v>
+        <v>7203772</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5187,19 +4607,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5226,37 +4636,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>88361993</v>
+        <v>88404442</v>
       </c>
       <c r="B40" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5266,10 +4671,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520785.553922729</v>
+        <v>520765</v>
       </c>
       <c r="R40" t="n">
-        <v>7203797.702376398</v>
+        <v>7203770</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5299,19 +4704,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5326,27 +4721,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Billy Lindblom, Alexina Brännlund, Emmy Ransgart, Mikael Sandström</t>
+          <t>Via Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>88362015</v>
+        <v>88404443</v>
       </c>
       <c r="B41" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5354,21 +4744,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5378,10 +4768,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520929.3000788022</v>
+        <v>520766</v>
       </c>
       <c r="R41" t="n">
-        <v>7203507.97325526</v>
+        <v>7203687</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5411,19 +4801,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5438,27 +4818,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Billy Lindblom, Alexina Brännlund, Emmy Ransgart, Mikael Sandström</t>
+          <t>Via Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>88404516</v>
+        <v>88404271</v>
       </c>
       <c r="B42" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5466,21 +4841,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5490,10 +4865,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521011.1740920344</v>
+        <v>521081</v>
       </c>
       <c r="R42" t="n">
-        <v>7203571.697948214</v>
+        <v>7203685</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5523,19 +4898,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5562,37 +4927,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>88362019</v>
+        <v>88362014</v>
       </c>
       <c r="B43" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5602,10 +4962,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520991.0557429698</v>
+        <v>520875</v>
       </c>
       <c r="R43" t="n">
-        <v>7203596.561818052</v>
+        <v>7203465</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5635,19 +4995,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5674,37 +5024,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>88362022</v>
+        <v>88362016</v>
       </c>
       <c r="B44" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5714,10 +5059,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521029.9637783722</v>
+        <v>520931</v>
       </c>
       <c r="R44" t="n">
-        <v>7203615.059566132</v>
+        <v>7203520</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5747,19 +5092,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5786,15 +5121,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>88404559</v>
+        <v>88404270</v>
       </c>
       <c r="B45" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5802,21 +5132,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>510</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5826,10 +5156,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>521036.6183579908</v>
+        <v>521081</v>
       </c>
       <c r="R45" t="n">
-        <v>7203634.178017432</v>
+        <v>7203685</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5859,19 +5189,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5898,15 +5218,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>88404517</v>
+        <v>88361992</v>
       </c>
       <c r="B46" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5914,21 +5229,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5938,10 +5253,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521016.3532085513</v>
+        <v>520795</v>
       </c>
       <c r="R46" t="n">
-        <v>7203619.625731232</v>
+        <v>7203775</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5971,19 +5286,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5998,49 +5303,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Via Yasmine Kindlund</t>
+          <t>Billy Lindblom, Alexina Brännlund, Emmy Ransgart, Mikael Sandström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>88404509</v>
+        <v>88404269</v>
       </c>
       <c r="B47" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6050,10 +5350,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>521157.3552198453</v>
+        <v>521081</v>
       </c>
       <c r="R47" t="n">
-        <v>7203002.636493819</v>
+        <v>7203685</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6083,19 +5383,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6122,37 +5412,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>88361994</v>
+        <v>88361993</v>
       </c>
       <c r="B48" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>2809</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6162,10 +5447,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>520783.382398433</v>
+        <v>520786</v>
       </c>
       <c r="R48" t="n">
-        <v>7203804.891655518</v>
+        <v>7203798</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6195,19 +5480,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6234,15 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>88362020</v>
+        <v>88362021</v>
       </c>
       <c r="B49" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6250,21 +5520,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>3242</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6274,10 +5544,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>520999.0401341406</v>
+        <v>521000</v>
       </c>
       <c r="R49" t="n">
-        <v>7203607.637160353</v>
+        <v>7203596</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6307,19 +5577,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6346,15 +5606,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>88362023</v>
+        <v>88362017</v>
       </c>
       <c r="B50" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6386,10 +5641,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>521147.0115594036</v>
+        <v>520935</v>
       </c>
       <c r="R50" t="n">
-        <v>7203744.299002188</v>
+        <v>7203524</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6419,19 +5674,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6458,37 +5703,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>88404441</v>
+        <v>88362023</v>
       </c>
       <c r="B51" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6498,10 +5738,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520761.9739616587</v>
+        <v>521147</v>
       </c>
       <c r="R51" t="n">
-        <v>7203771.687190244</v>
+        <v>7203744</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6531,19 +5771,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6558,49 +5788,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Via Yasmine Kindlund</t>
+          <t>Billy Lindblom, Alexina Brännlund, Emmy Ransgart, Mikael Sandström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>88404271</v>
+        <v>88362022</v>
       </c>
       <c r="B52" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6610,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>521080.8142190702</v>
+        <v>521030</v>
       </c>
       <c r="R52" t="n">
-        <v>7203684.922787505</v>
+        <v>7203615</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6643,19 +5868,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6670,27 +5885,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Via Yasmine Kindlund</t>
+          <t>Billy Lindblom, Alexina Brännlund, Emmy Ransgart, Mikael Sandström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>88404442</v>
+        <v>88362019</v>
       </c>
       <c r="B53" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6698,21 +5908,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6722,10 +5932,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520765.3770642996</v>
+        <v>520991</v>
       </c>
       <c r="R53" t="n">
-        <v>7203770.439471498</v>
+        <v>7203597</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6755,19 +5965,9 @@
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6782,575 +5982,15 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Via Yasmine Kindlund</t>
+          <t>Billy Lindblom, Alexina Brännlund, Emmy Ransgart, Mikael Sandström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>88362018</v>
-      </c>
-      <c r="B54" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>864</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Hypogymnia bitteri</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Saxnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>520965.4198347409</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7203561.204758866</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Billy Lindblom</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Billy Lindblom, Alexina Brännlund, Emmy Ransgart, Mikael Sandström</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>88361992</v>
-      </c>
-      <c r="B55" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Saxnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>520794.6231028006</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7203774.880853981</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Billy Lindblom</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Billy Lindblom, Alexina Brännlund, Emmy Ransgart, Mikael Sandström</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>88362016</v>
-      </c>
-      <c r="B56" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Saxnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>520930.9142135374</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7203519.851766488</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Billy Lindblom</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Billy Lindblom, Alexina Brännlund, Emmy Ransgart, Mikael Sandström</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>88404269</v>
-      </c>
-      <c r="B57" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>1506</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Ostticka</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Skeletocutis odora</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Saxnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>521080.8142190702</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7203684.922787505</v>
-      </c>
-      <c r="S57" t="n">
-        <v>10</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Yasmine Kindlund</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Via Yasmine Kindlund</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>88362017</v>
-      </c>
-      <c r="B58" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Saxnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>520935.130670684</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7203523.695761246</v>
-      </c>
-      <c r="S58" t="n">
-        <v>10</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2020-09-20</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Billy Lindblom</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Billy Lindblom, Alexina Brännlund, Emmy Ransgart, Mikael Sandström</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
